--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-09-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_29-09-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff60c921eb5+80197]
+	GetHandleVerifier [0x0x7ff60c921f10+80288]
+	(No symbol) [0x0x7ff60c6a02fa]
+	(No symbol) [0x0x7ff60c6f7cd7]
+	(No symbol) [0x0x7ff60c6f7f9c]
+	(No symbol) [0x0x7ff60c74ba87]
+	(No symbol) [0x0x7ff60c7203bf]
+	(No symbol) [0x0x7ff60c7487fb]
+	(No symbol) [0x0x7ff60c720153]
+	(No symbol) [0x0x7ff60c6e8b02]
+	(No symbol) [0x0x7ff60c6e98d3]
+	GetHandleVerifier [0x0x7ff60cbde83d+2949837]
+	GetHandleVerifier [0x0x7ff60cbd8c6a+2926330]
+	GetHandleVerifier [0x0x7ff60cbf86c7+3055959]
+	GetHandleVerifier [0x0x7ff60c93cfee+191102]
+	GetHandleVerifier [0x0x7ff60c9450af+224063]
+	GetHandleVerifier [0x0x7ff60c92af64+117236]
+	GetHandleVerifier [0x0x7ff60c92b119+117673]
+	GetHandleVerifier [0x0x7ff60c9110a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff60c921eb5+80197]
+	GetHandleVerifier [0x0x7ff60c921f10+80288]
+	(No symbol) [0x0x7ff60c6a02fa]
+	(No symbol) [0x0x7ff60c6f7cd7]
+	(No symbol) [0x0x7ff60c6f7f9c]
+	(No symbol) [0x0x7ff60c74ba87]
+	(No symbol) [0x0x7ff60c7203bf]
+	(No symbol) [0x0x7ff60c7487fb]
+	(No symbol) [0x0x7ff60c720153]
+	(No symbol) [0x0x7ff60c6e8b02]
+	(No symbol) [0x0x7ff60c6e98d3]
+	GetHandleVerifier [0x0x7ff60cbde83d+2949837]
+	GetHandleVerifier [0x0x7ff60cbd8c6a+2926330]
+	GetHandleVerifier [0x0x7ff60cbf86c7+3055959]
+	GetHandleVerifier [0x0x7ff60c93cfee+191102]
+	GetHandleVerifier [0x0x7ff60c9450af+224063]
+	GetHandleVerifier [0x0x7ff60c92af64+117236]
+	GetHandleVerifier [0x0x7ff60c92b119+117673]
+	GetHandleVerifier [0x0x7ff60c9110a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -780,12 +780,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff60c921eb5+80197]
+	GetHandleVerifier [0x0x7ff60c921f10+80288]
+	(No symbol) [0x0x7ff60c6a02fa]
+	(No symbol) [0x0x7ff60c6f7cd7]
+	(No symbol) [0x0x7ff60c6f7f9c]
+	(No symbol) [0x0x7ff60c74ba87]
+	(No symbol) [0x0x7ff60c7203bf]
+	(No symbol) [0x0x7ff60c7487fb]
+	(No symbol) [0x0x7ff60c720153]
+	(No symbol) [0x0x7ff60c6e8b02]
+	(No symbol) [0x0x7ff60c6e98d3]
+	GetHandleVerifier [0x0x7ff60cbde83d+2949837]
+	GetHandleVerifier [0x0x7ff60cbd8c6a+2926330]
+	GetHandleVerifier [0x0x7ff60cbf86c7+3055959]
+	GetHandleVerifier [0x0x7ff60c93cfee+191102]
+	GetHandleVerifier [0x0x7ff60c9450af+224063]
+	GetHandleVerifier [0x0x7ff60c92af64+117236]
+	GetHandleVerifier [0x0x7ff60c92b119+117673]
+	GetHandleVerifier [0x0x7ff60c9110a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: 522 Server Error: &lt;none&gt; for url: https://www.windwarrior.com/about-honor/</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>£20.49 presale price: £31.68</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff6401b1eb5+80197]
+	GetHandleVerifier [0x0x7ff6401b1f10+80288]
+	(No symbol) [0x0x7ff63ff302fa]
+	(No symbol) [0x0x7ff63ff87cd7]
+	(No symbol) [0x0x7ff63ff87f9c]
+	(No symbol) [0x0x7ff63ffdba87]
+	(No symbol) [0x0x7ff63ffb03bf]
+	(No symbol) [0x0x7ff63ffd87fb]
+	(No symbol) [0x0x7ff63ffb0153]
+	(No symbol) [0x0x7ff63ff78b02]
+	(No symbol) [0x0x7ff63ff798d3]
+	GetHandleVerifier [0x0x7ff64046e83d+2949837]
+	GetHandleVerifier [0x0x7ff640468c6a+2926330]
+	GetHandleVerifier [0x0x7ff6404886c7+3055959]
+	GetHandleVerifier [0x0x7ff6401ccfee+191102]
+	GetHandleVerifier [0x0x7ff6401d50af+224063]
+	GetHandleVerifier [0x0x7ff6401baf64+117236]
+	GetHandleVerifier [0x0x7ff6401bb119+117673]
+	GetHandleVerifier [0x0x7ff6401a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff6401b1eb5+80197]
+	GetHandleVerifier [0x0x7ff6401b1f10+80288]
+	(No symbol) [0x0x7ff63ff302fa]
+	(No symbol) [0x0x7ff63ff87cd7]
+	(No symbol) [0x0x7ff63ff87f9c]
+	(No symbol) [0x0x7ff63ffdba87]
+	(No symbol) [0x0x7ff63ffb03bf]
+	(No symbol) [0x0x7ff63ffd87fb]
+	(No symbol) [0x0x7ff63ffb0153]
+	(No symbol) [0x0x7ff63ff78b02]
+	(No symbol) [0x0x7ff63ff798d3]
+	GetHandleVerifier [0x0x7ff64046e83d+2949837]
+	GetHandleVerifier [0x0x7ff640468c6a+2926330]
+	GetHandleVerifier [0x0x7ff6404886c7+3055959]
+	GetHandleVerifier [0x0x7ff6401ccfee+191102]
+	GetHandleVerifier [0x0x7ff6401d50af+224063]
+	GetHandleVerifier [0x0x7ff6401baf64+117236]
+	GetHandleVerifier [0x0x7ff6401bb119+117673]
+	GetHandleVerifier [0x0x7ff6401a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff6401b1eb5+80197]
+	GetHandleVerifier [0x0x7ff6401b1f10+80288]
+	(No symbol) [0x0x7ff63ff302fa]
+	(No symbol) [0x0x7ff63ff87cd7]
+	(No symbol) [0x0x7ff63ff87f9c]
+	(No symbol) [0x0x7ff63ffdba87]
+	(No symbol) [0x0x7ff63ffb03bf]
+	(No symbol) [0x0x7ff63ffd87fb]
+	(No symbol) [0x0x7ff63ffb0153]
+	(No symbol) [0x0x7ff63ff78b02]
+	(No symbol) [0x0x7ff63ff798d3]
+	GetHandleVerifier [0x0x7ff64046e83d+2949837]
+	GetHandleVerifier [0x0x7ff640468c6a+2926330]
+	GetHandleVerifier [0x0x7ff6404886c7+3055959]
+	GetHandleVerifier [0x0x7ff6401ccfee+191102]
+	GetHandleVerifier [0x0x7ff6401d50af+224063]
+	GetHandleVerifier [0x0x7ff6401baf64+117236]
+	GetHandleVerifier [0x0x7ff6401bb119+117673]
+	GetHandleVerifier [0x0x7ff6401a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1264,17 +1264,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff6401b1eb5+80197]
+	GetHandleVerifier [0x0x7ff6401b1f10+80288]
+	(No symbol) [0x0x7ff63ff302fa]
+	(No symbol) [0x0x7ff63ff87cd7]
+	(No symbol) [0x0x7ff63ff87f9c]
+	(No symbol) [0x0x7ff63ffdba87]
+	(No symbol) [0x0x7ff63ffb03bf]
+	(No symbol) [0x0x7ff63ffd87fb]
+	(No symbol) [0x0x7ff63ffb0153]
+	(No symbol) [0x0x7ff63ff78b02]
+	(No symbol) [0x0x7ff63ff798d3]
+	GetHandleVerifier [0x0x7ff64046e83d+2949837]
+	GetHandleVerifier [0x0x7ff640468c6a+2926330]
+	GetHandleVerifier [0x0x7ff6404886c7+3055959]
+	GetHandleVerifier [0x0x7ff6401ccfee+191102]
+	GetHandleVerifier [0x0x7ff6401d50af+224063]
+	GetHandleVerifier [0x0x7ff6401baf64+117236]
+	GetHandleVerifier [0x0x7ff6401bb119+117673]
+	GetHandleVerifier [0x0x7ff6401a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff77e4a1eb5+80197]
+	GetHandleVerifier [0x0x7ff77e4a1f10+80288]
+	(No symbol) [0x0x7ff77e2202fa]
+	(No symbol) [0x0x7ff77e277cd7]
+	(No symbol) [0x0x7ff77e277f9c]
+	(No symbol) [0x0x7ff77e2cba87]
+	(No symbol) [0x0x7ff77e2a03bf]
+	(No symbol) [0x0x7ff77e2c87fb]
+	(No symbol) [0x0x7ff77e2a0153]
+	(No symbol) [0x0x7ff77e268b02]
+	(No symbol) [0x0x7ff77e2698d3]
+	GetHandleVerifier [0x0x7ff77e75e83d+2949837]
+	GetHandleVerifier [0x0x7ff77e758c6a+2926330]
+	GetHandleVerifier [0x0x7ff77e7786c7+3055959]
+	GetHandleVerifier [0x0x7ff77e4bcfee+191102]
+	GetHandleVerifier [0x0x7ff77e4c50af+224063]
+	GetHandleVerifier [0x0x7ff77e4aaf64+117236]
+	GetHandleVerifier [0x0x7ff77e4ab119+117673]
+	GetHandleVerifier [0x0x7ff77e4910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff77e4a1eb5+80197]
+	GetHandleVerifier [0x0x7ff77e4a1f10+80288]
+	(No symbol) [0x0x7ff77e2202fa]
+	(No symbol) [0x0x7ff77e277cd7]
+	(No symbol) [0x0x7ff77e277f9c]
+	(No symbol) [0x0x7ff77e2cba87]
+	(No symbol) [0x0x7ff77e2a03bf]
+	(No symbol) [0x0x7ff77e2c87fb]
+	(No symbol) [0x0x7ff77e2a0153]
+	(No symbol) [0x0x7ff77e268b02]
+	(No symbol) [0x0x7ff77e2698d3]
+	GetHandleVerifier [0x0x7ff77e75e83d+2949837]
+	GetHandleVerifier [0x0x7ff77e758c6a+2926330]
+	GetHandleVerifier [0x0x7ff77e7786c7+3055959]
+	GetHandleVerifier [0x0x7ff77e4bcfee+191102]
+	GetHandleVerifier [0x0x7ff77e4c50af+224063]
+	GetHandleVerifier [0x0x7ff77e4aaf64+117236]
+	GetHandleVerifier [0x0x7ff77e4ab119+117673]
+	GetHandleVerifier [0x0x7ff77e4910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff77e4a1eb5+80197]
+	GetHandleVerifier [0x0x7ff77e4a1f10+80288]
+	(No symbol) [0x0x7ff77e2202fa]
+	(No symbol) [0x0x7ff77e277cd7]
+	(No symbol) [0x0x7ff77e277f9c]
+	(No symbol) [0x0x7ff77e2cba87]
+	(No symbol) [0x0x7ff77e2a03bf]
+	(No symbol) [0x0x7ff77e2c87fb]
+	(No symbol) [0x0x7ff77e2a0153]
+	(No symbol) [0x0x7ff77e268b02]
+	(No symbol) [0x0x7ff77e2698d3]
+	GetHandleVerifier [0x0x7ff77e75e83d+2949837]
+	GetHandleVerifier [0x0x7ff77e758c6a+2926330]
+	GetHandleVerifier [0x0x7ff77e7786c7+3055959]
+	GetHandleVerifier [0x0x7ff77e4bcfee+191102]
+	GetHandleVerifier [0x0x7ff77e4c50af+224063]
+	GetHandleVerifier [0x0x7ff77e4aaf64+117236]
+	GetHandleVerifier [0x0x7ff77e4ab119+117673]
+	GetHandleVerifier [0x0x7ff77e4910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff77e4a1eb5+80197]
+	GetHandleVerifier [0x0x7ff77e4a1f10+80288]
+	(No symbol) [0x0x7ff77e2202fa]
+	(No symbol) [0x0x7ff77e277cd7]
+	(No symbol) [0x0x7ff77e277f9c]
+	(No symbol) [0x0x7ff77e2cba87]
+	(No symbol) [0x0x7ff77e2a03bf]
+	(No symbol) [0x0x7ff77e2c87fb]
+	(No symbol) [0x0x7ff77e2a0153]
+	(No symbol) [0x0x7ff77e268b02]
+	(No symbol) [0x0x7ff77e2698d3]
+	GetHandleVerifier [0x0x7ff77e75e83d+2949837]
+	GetHandleVerifier [0x0x7ff77e758c6a+2926330]
+	GetHandleVerifier [0x0x7ff77e7786c7+3055959]
+	GetHandleVerifier [0x0x7ff77e4bcfee+191102]
+	GetHandleVerifier [0x0x7ff77e4c50af+224063]
+	GetHandleVerifier [0x0x7ff77e4aaf64+117236]
+	GetHandleVerifier [0x0x7ff77e4ab119+117673]
+	GetHandleVerifier [0x0x7ff77e4910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1869,17 +1869,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff77e4a1eb5+80197]
+	GetHandleVerifier [0x0x7ff77e4a1f10+80288]
+	(No symbol) [0x0x7ff77e2202fa]
+	(No symbol) [0x0x7ff77e277cd7]
+	(No symbol) [0x0x7ff77e277f9c]
+	(No symbol) [0x0x7ff77e2cba87]
+	(No symbol) [0x0x7ff77e2a03bf]
+	(No symbol) [0x0x7ff77e2c87fb]
+	(No symbol) [0x0x7ff77e2a0153]
+	(No symbol) [0x0x7ff77e268b02]
+	(No symbol) [0x0x7ff77e2698d3]
+	GetHandleVerifier [0x0x7ff77e75e83d+2949837]
+	GetHandleVerifier [0x0x7ff77e758c6a+2926330]
+	GetHandleVerifier [0x0x7ff77e7786c7+3055959]
+	GetHandleVerifier [0x0x7ff77e4bcfee+191102]
+	GetHandleVerifier [0x0x7ff77e4c50af+224063]
+	GetHandleVerifier [0x0x7ff77e4aaf64+117236]
+	GetHandleVerifier [0x0x7ff77e4ab119+117673]
+	GetHandleVerifier [0x0x7ff77e4910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>£51.25</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff77e4a1eb5+80197]
+	GetHandleVerifier [0x0x7ff77e4a1f10+80288]
+	(No symbol) [0x0x7ff77e2202fa]
+	(No symbol) [0x0x7ff77e277cd7]
+	(No symbol) [0x0x7ff77e277f9c]
+	(No symbol) [0x0x7ff77e2cba87]
+	(No symbol) [0x0x7ff77e2a03bf]
+	(No symbol) [0x0x7ff77e2c87fb]
+	(No symbol) [0x0x7ff77e2a0153]
+	(No symbol) [0x0x7ff77e268b02]
+	(No symbol) [0x0x7ff77e2698d3]
+	GetHandleVerifier [0x0x7ff77e75e83d+2949837]
+	GetHandleVerifier [0x0x7ff77e758c6a+2926330]
+	GetHandleVerifier [0x0x7ff77e7786c7+3055959]
+	GetHandleVerifier [0x0x7ff77e4bcfee+191102]
+	GetHandleVerifier [0x0x7ff77e4c50af+224063]
+	GetHandleVerifier [0x0x7ff77e4aaf64+117236]
+	GetHandleVerifier [0x0x7ff77e4ab119+117673]
+	GetHandleVerifier [0x0x7ff77e4910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff77e4a1eb5+80197]
+	GetHandleVerifier [0x0x7ff77e4a1f10+80288]
+	(No symbol) [0x0x7ff77e2202fa]
+	(No symbol) [0x0x7ff77e277cd7]
+	(No symbol) [0x0x7ff77e277f9c]
+	(No symbol) [0x0x7ff77e2cba87]
+	(No symbol) [0x0x7ff77e2a03bf]
+	(No symbol) [0x0x7ff77e2c87fb]
+	(No symbol) [0x0x7ff77e2a0153]
+	(No symbol) [0x0x7ff77e268b02]
+	(No symbol) [0x0x7ff77e2698d3]
+	GetHandleVerifier [0x0x7ff77e75e83d+2949837]
+	GetHandleVerifier [0x0x7ff77e758c6a+2926330]
+	GetHandleVerifier [0x0x7ff77e7786c7+3055959]
+	GetHandleVerifier [0x0x7ff77e4bcfee+191102]
+	GetHandleVerifier [0x0x7ff77e4c50af+224063]
+	GetHandleVerifier [0x0x7ff77e4aaf64+117236]
+	GetHandleVerifier [0x0x7ff77e4ab119+117673]
+	GetHandleVerifier [0x0x7ff77e4910a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£40.62</t>
+          <t>£40.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff70bb61eb5+80197]
+	GetHandleVerifier [0x0x7ff70bb61f10+80288]
+	(No symbol) [0x0x7ff70b8e02fa]
+	(No symbol) [0x0x7ff70b937cd7]
+	(No symbol) [0x0x7ff70b937f9c]
+	(No symbol) [0x0x7ff70b98ba87]
+	(No symbol) [0x0x7ff70b9603bf]
+	(No symbol) [0x0x7ff70b9887fb]
+	(No symbol) [0x0x7ff70b960153]
+	(No symbol) [0x0x7ff70b928b02]
+	(No symbol) [0x0x7ff70b9298d3]
+	GetHandleVerifier [0x0x7ff70be1e83d+2949837]
+	GetHandleVerifier [0x0x7ff70be18c6a+2926330]
+	GetHandleVerifier [0x0x7ff70be386c7+3055959]
+	GetHandleVerifier [0x0x7ff70bb7cfee+191102]
+	GetHandleVerifier [0x0x7ff70bb850af+224063]
+	GetHandleVerifier [0x0x7ff70bb6af64+117236]
+	GetHandleVerifier [0x0x7ff70bb6b119+117673]
+	GetHandleVerifier [0x0x7ff70bb510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff700811eb5+80197]
+	GetHandleVerifier [0x0x7ff700811f10+80288]
+	(No symbol) [0x0x7ff7005902fa]
+	(No symbol) [0x0x7ff7005e7cd7]
+	(No symbol) [0x0x7ff7005e7f9c]
+	(No symbol) [0x0x7ff70063ba87]
+	(No symbol) [0x0x7ff7006103bf]
+	(No symbol) [0x0x7ff7006387fb]
+	(No symbol) [0x0x7ff700610153]
+	(No symbol) [0x0x7ff7005d8b02]
+	(No symbol) [0x0x7ff7005d98d3]
+	GetHandleVerifier [0x0x7ff700ace83d+2949837]
+	GetHandleVerifier [0x0x7ff700ac8c6a+2926330]
+	GetHandleVerifier [0x0x7ff700ae86c7+3055959]
+	GetHandleVerifier [0x0x7ff70082cfee+191102]
+	GetHandleVerifier [0x0x7ff7008350af+224063]
+	GetHandleVerifier [0x0x7ff70081af64+117236]
+	GetHandleVerifier [0x0x7ff70081b119+117673]
+	GetHandleVerifier [0x0x7ff7008010a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff700811eb5+80197]
+	GetHandleVerifier [0x0x7ff700811f10+80288]
+	(No symbol) [0x0x7ff7005902fa]
+	(No symbol) [0x0x7ff7005e7cd7]
+	(No symbol) [0x0x7ff7005e7f9c]
+	(No symbol) [0x0x7ff70063ba87]
+	(No symbol) [0x0x7ff7006103bf]
+	(No symbol) [0x0x7ff7006387fb]
+	(No symbol) [0x0x7ff700610153]
+	(No symbol) [0x0x7ff7005d8b02]
+	(No symbol) [0x0x7ff7005d98d3]
+	GetHandleVerifier [0x0x7ff700ace83d+2949837]
+	GetHandleVerifier [0x0x7ff700ac8c6a+2926330]
+	GetHandleVerifier [0x0x7ff700ae86c7+3055959]
+	GetHandleVerifier [0x0x7ff70082cfee+191102]
+	GetHandleVerifier [0x0x7ff7008350af+224063]
+	GetHandleVerifier [0x0x7ff70081af64+117236]
+	GetHandleVerifier [0x0x7ff70081b119+117673]
+	GetHandleVerifier [0x0x7ff7008010a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff700811eb5+80197]
+	GetHandleVerifier [0x0x7ff700811f10+80288]
+	(No symbol) [0x0x7ff7005902fa]
+	(No symbol) [0x0x7ff7005e7cd7]
+	(No symbol) [0x0x7ff7005e7f9c]
+	(No symbol) [0x0x7ff70063ba87]
+	(No symbol) [0x0x7ff7006103bf]
+	(No symbol) [0x0x7ff7006387fb]
+	(No symbol) [0x0x7ff700610153]
+	(No symbol) [0x0x7ff7005d8b02]
+	(No symbol) [0x0x7ff7005d98d3]
+	GetHandleVerifier [0x0x7ff700ace83d+2949837]
+	GetHandleVerifier [0x0x7ff700ac8c6a+2926330]
+	GetHandleVerifier [0x0x7ff700ae86c7+3055959]
+	GetHandleVerifier [0x0x7ff70082cfee+191102]
+	GetHandleVerifier [0x0x7ff7008350af+224063]
+	GetHandleVerifier [0x0x7ff70081af64+117236]
+	GetHandleVerifier [0x0x7ff70081b119+117673]
+	GetHandleVerifier [0x0x7ff7008010a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff700811eb5+80197]
+	GetHandleVerifier [0x0x7ff700811f10+80288]
+	(No symbol) [0x0x7ff7005902fa]
+	(No symbol) [0x0x7ff7005e7cd7]
+	(No symbol) [0x0x7ff7005e7f9c]
+	(No symbol) [0x0x7ff70063ba87]
+	(No symbol) [0x0x7ff7006103bf]
+	(No symbol) [0x0x7ff7006387fb]
+	(No symbol) [0x0x7ff700610153]
+	(No symbol) [0x0x7ff7005d8b02]
+	(No symbol) [0x0x7ff7005d98d3]
+	GetHandleVerifier [0x0x7ff700ace83d+2949837]
+	GetHandleVerifier [0x0x7ff700ac8c6a+2926330]
+	GetHandleVerifier [0x0x7ff700ae86c7+3055959]
+	GetHandleVerifier [0x0x7ff70082cfee+191102]
+	GetHandleVerifier [0x0x7ff7008350af+224063]
+	GetHandleVerifier [0x0x7ff70081af64+117236]
+	GetHandleVerifier [0x0x7ff70081b119+117673]
+	GetHandleVerifier [0x0x7ff7008010a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff700811eb5+80197]
+	GetHandleVerifier [0x0x7ff700811f10+80288]
+	(No symbol) [0x0x7ff7005902fa]
+	(No symbol) [0x0x7ff7005e7cd7]
+	(No symbol) [0x0x7ff7005e7f9c]
+	(No symbol) [0x0x7ff70063ba87]
+	(No symbol) [0x0x7ff7006103bf]
+	(No symbol) [0x0x7ff7006387fb]
+	(No symbol) [0x0x7ff700610153]
+	(No symbol) [0x0x7ff7005d8b02]
+	(No symbol) [0x0x7ff7005d98d3]
+	GetHandleVerifier [0x0x7ff700ace83d+2949837]
+	GetHandleVerifier [0x0x7ff700ac8c6a+2926330]
+	GetHandleVerifier [0x0x7ff700ae86c7+3055959]
+	GetHandleVerifier [0x0x7ff70082cfee+191102]
+	GetHandleVerifier [0x0x7ff7008350af+224063]
+	GetHandleVerifier [0x0x7ff70081af64+117236]
+	GetHandleVerifier [0x0x7ff70081b119+117673]
+	GetHandleVerifier [0x0x7ff7008010a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
